--- a/tests/data/output/test_report_KapJI_cgc.xlsx
+++ b/tests/data/output/test_report_KapJI_cgc.xlsx
@@ -1122,7 +1122,7 @@
       <c r="L23" s="5"/>
       <c r="N23" s="6"/>
       <c r="O23" s="5">
-        <v>0</v>
+        <v>0E-28</v>
       </c>
       <c r="P23" s="4">
         <v>104</v>
@@ -1163,7 +1163,7 @@
       <c r="L24" s="5"/>
       <c r="N24" s="6"/>
       <c r="O24" s="5">
-        <v>0</v>
+        <v>0E-28</v>
       </c>
       <c r="P24" s="4">
         <v>159</v>
